--- a/artfynd/A 31704-2026 artfynd.xlsx
+++ b/artfynd/A 31704-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,138 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311731</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135579790</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93283</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Naisjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>828765</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7401297</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135579790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31704-2026 artfynd.xlsx
+++ b/artfynd/A 31704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135311731</v>
       </c>
       <c r="B2" t="n">
-        <v>93265</v>
+        <v>93307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579790</v>
       </c>
       <c r="B3" t="n">
-        <v>93283</v>
+        <v>93325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31704-2026 artfynd.xlsx
+++ b/artfynd/A 31704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135311731</v>
       </c>
       <c r="B2" t="n">
-        <v>93307</v>
+        <v>93334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579790</v>
       </c>
       <c r="B3" t="n">
-        <v>93325</v>
+        <v>93352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31704-2026 artfynd.xlsx
+++ b/artfynd/A 31704-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135311731</v>
       </c>
       <c r="B2" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579790</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
